--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11265" uniqueCount="3211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11266" uniqueCount="3211">
   <si>
     <t>First Name</t>
   </si>
@@ -47914,7 +47914,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2065" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2065" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2065" t="s">
         <v>146</v>
       </c>
@@ -47932,7 +47932,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2066" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2066" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2066" t="s">
         <v>2477</v>
       </c>
@@ -47950,7 +47950,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="2067" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2067" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2067" t="s">
         <v>1755</v>
       </c>
@@ -47968,7 +47968,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="2068" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2068" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2068" t="s">
         <v>772</v>
       </c>
@@ -47986,7 +47986,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="2069" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2069" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2069" t="s">
         <v>171</v>
       </c>
@@ -48004,7 +48004,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="2070" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2070" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2070" t="s">
         <v>2458</v>
       </c>
@@ -48022,7 +48022,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="2071" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2071" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2071" t="s">
         <v>2460</v>
       </c>
@@ -48040,7 +48040,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="2072" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2072" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2072" t="s">
         <v>1161</v>
       </c>
@@ -48058,7 +48058,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="2073" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2073" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2073" t="s">
         <v>2461</v>
       </c>
@@ -48076,7 +48076,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="2074" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2074" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2074" t="s">
         <v>311</v>
       </c>
@@ -48094,7 +48094,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="2075" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2075" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2075" t="s">
         <v>794</v>
       </c>
@@ -48112,7 +48112,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="2076" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2076" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2076" t="s">
         <v>943</v>
       </c>
@@ -48130,7 +48130,7 @@
         <v>3176</v>
       </c>
     </row>
-    <row r="2077" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2077" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2077" t="s">
         <v>819</v>
       </c>
@@ -48148,7 +48148,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="2078" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2078" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2078" t="s">
         <v>1431</v>
       </c>
@@ -48166,7 +48166,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="2079" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2079" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2079" t="s">
         <v>311</v>
       </c>
@@ -48184,7 +48184,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="2080" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2080" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2080" t="s">
         <v>2495</v>
       </c>
@@ -48200,6 +48200,9 @@
       </c>
       <c r="E2080" t="s">
         <v>2117</v>
+      </c>
+      <c r="F2080" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2081" spans="1:6" x14ac:dyDescent="0.25">

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11266" uniqueCount="3211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11299" uniqueCount="3221">
   <si>
     <t>First Name</t>
   </si>
@@ -9661,6 +9661,36 @@
   </si>
   <si>
     <t>Tony</t>
+  </si>
+  <si>
+    <t>Methven</t>
+  </si>
+  <si>
+    <t>Akkeel</t>
+  </si>
+  <si>
+    <t>Anzaar</t>
+  </si>
+  <si>
+    <t>Frgus</t>
+  </si>
+  <si>
+    <t>Emmett</t>
+  </si>
+  <si>
+    <t>Saranraj</t>
+  </si>
+  <si>
+    <t>Sohil Sai</t>
+  </si>
+  <si>
+    <t>Bande</t>
+  </si>
+  <si>
+    <t>Doak</t>
+  </si>
+  <si>
+    <t>Arran</t>
   </si>
 </sst>
 </file>
@@ -10482,7 +10512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3693"/>
+  <dimension ref="A1:F3704"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -76677,7 +76707,7 @@
         <v>3170</v>
       </c>
       <c r="C3647" t="str">
-        <f t="shared" ref="C3647:C3693" si="57">PROPER(A3647&amp; " "&amp;B3647)</f>
+        <f t="shared" ref="C3647:C3704" si="57">PROPER(A3647&amp; " "&amp;B3647)</f>
         <v>Oliver Funnell</v>
       </c>
       <c r="D3647" s="5">
@@ -77469,56 +77499,254 @@
     </row>
     <row r="3691" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3691" t="s">
-        <v>3202</v>
+        <v>350</v>
       </c>
       <c r="B3691" t="s">
-        <v>3203</v>
+        <v>266</v>
       </c>
       <c r="C3691" t="str">
         <f t="shared" si="57"/>
-        <v>Lokesh Gehani</v>
+        <v>Noah Bell</v>
       </c>
       <c r="D3691" s="5">
         <v>46219</v>
       </c>
       <c r="E3691" t="s">
-        <v>1519</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="3692" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3692" t="s">
-        <v>355</v>
+        <v>3202</v>
       </c>
       <c r="B3692" t="s">
-        <v>3209</v>
+        <v>3203</v>
       </c>
       <c r="C3692" t="str">
         <f t="shared" si="57"/>
-        <v>Harry Murtagh</v>
+        <v>Lokesh Gehani</v>
       </c>
       <c r="D3692" s="5">
         <v>46219</v>
       </c>
       <c r="E3692" t="s">
-        <v>1799</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="3693" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3693" t="s">
-        <v>3210</v>
+        <v>162</v>
       </c>
       <c r="B3693" t="s">
-        <v>1280</v>
+        <v>3211</v>
       </c>
       <c r="C3693" t="str">
         <f t="shared" si="57"/>
-        <v>Tony Walsh</v>
+        <v>David Methven</v>
       </c>
       <c r="D3693" s="5">
         <v>46219</v>
       </c>
       <c r="E3693" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="3694" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3694" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3694" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C3694" t="str">
+        <f t="shared" si="57"/>
+        <v>Harry Murtagh</v>
+      </c>
+      <c r="D3694" s="5">
+        <v>46219</v>
+      </c>
+      <c r="E3694" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="3695" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3695" t="s">
+        <v>3210</v>
+      </c>
+      <c r="B3695" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C3695" t="str">
+        <f t="shared" si="57"/>
+        <v>Tony Walsh</v>
+      </c>
+      <c r="D3695" s="5">
+        <v>46219</v>
+      </c>
+      <c r="E3695" t="s">
         <v>1412</v>
+      </c>
+    </row>
+    <row r="3696" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3696" t="s">
+        <v>3212</v>
+      </c>
+      <c r="B3696" t="s">
+        <v>3213</v>
+      </c>
+      <c r="C3696" t="str">
+        <f t="shared" si="57"/>
+        <v>Akkeel Anzaar</v>
+      </c>
+      <c r="D3696" s="5">
+        <v>46220</v>
+      </c>
+      <c r="E3696" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="3697" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3697" t="s">
+        <v>562</v>
+      </c>
+      <c r="B3697" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C3697" t="str">
+        <f t="shared" si="57"/>
+        <v>Leo Benson</v>
+      </c>
+      <c r="D3697" s="5">
+        <v>46220</v>
+      </c>
+      <c r="E3697" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="3698" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3698" t="s">
+        <v>395</v>
+      </c>
+      <c r="B3698" t="s">
+        <v>2596</v>
+      </c>
+      <c r="C3698" t="str">
+        <f t="shared" si="57"/>
+        <v>Lewis Darcy</v>
+      </c>
+      <c r="D3698" s="5">
+        <v>46220</v>
+      </c>
+      <c r="E3698" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="3699" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3699" t="s">
+        <v>3214</v>
+      </c>
+      <c r="B3699" t="s">
+        <v>3215</v>
+      </c>
+      <c r="C3699" t="str">
+        <f t="shared" si="57"/>
+        <v>Frgus Emmett</v>
+      </c>
+      <c r="D3699" s="5">
+        <v>46220</v>
+      </c>
+      <c r="E3699" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="3700" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3700" t="s">
+        <v>3216</v>
+      </c>
+      <c r="B3700" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3700" t="str">
+        <f t="shared" si="57"/>
+        <v>Saranraj Krishnan</v>
+      </c>
+      <c r="D3700" s="5">
+        <v>46220</v>
+      </c>
+      <c r="E3700" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="3701" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3701" t="s">
+        <v>328</v>
+      </c>
+      <c r="B3701" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C3701" t="str">
+        <f t="shared" si="57"/>
+        <v>Gareth Leckey</v>
+      </c>
+      <c r="D3701" s="5">
+        <v>46220</v>
+      </c>
+      <c r="E3701" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="3702" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3702" t="s">
+        <v>3217</v>
+      </c>
+      <c r="B3702" t="s">
+        <v>3218</v>
+      </c>
+      <c r="C3702" t="str">
+        <f t="shared" si="57"/>
+        <v>Sohil Sai Bande</v>
+      </c>
+      <c r="D3702" s="5">
+        <v>46221</v>
+      </c>
+      <c r="E3702" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="3703" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3703" t="s">
+        <v>901</v>
+      </c>
+      <c r="B3703" t="s">
+        <v>3219</v>
+      </c>
+      <c r="C3703" t="str">
+        <f t="shared" si="57"/>
+        <v>Neil Doak</v>
+      </c>
+      <c r="D3703" s="5">
+        <v>46221</v>
+      </c>
+      <c r="E3703" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="3704" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3704" t="s">
+        <v>3220</v>
+      </c>
+      <c r="B3704" t="s">
+        <v>432</v>
+      </c>
+      <c r="C3704" t="str">
+        <f t="shared" si="57"/>
+        <v>Arran Scott</v>
+      </c>
+      <c r="D3704" s="5">
+        <v>46221</v>
+      </c>
+      <c r="E3704" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -12,11 +12,11 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17580"/>
   </bookViews>
   <sheets>
-    <sheet name="NCU_Registered_Players_07-07-26" sheetId="1" r:id="rId1"/>
+    <sheet name="NCU_Registered_Players_20-07-26" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NCU_Registered_Players_07-07-26'!$A$1:$F$3409</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NCU_Registered_Players_20-07-26'!$A$1:$F$3409</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11299" uniqueCount="3221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11311" uniqueCount="3224">
   <si>
     <t>First Name</t>
   </si>
@@ -9691,6 +9691,15 @@
   </si>
   <si>
     <t>Arran</t>
+  </si>
+  <si>
+    <t>Skilling</t>
+  </si>
+  <si>
+    <t>Domonikibau</t>
+  </si>
+  <si>
+    <t>Mclawrence</t>
   </si>
 </sst>
 </file>
@@ -10512,7 +10521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3704"/>
+  <dimension ref="A1:F3708"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -76707,7 +76716,7 @@
         <v>3170</v>
       </c>
       <c r="C3647" t="str">
-        <f t="shared" ref="C3647:C3704" si="57">PROPER(A3647&amp; " "&amp;B3647)</f>
+        <f t="shared" ref="C3647:C3708" si="57">PROPER(A3647&amp; " "&amp;B3647)</f>
         <v>Oliver Funnell</v>
       </c>
       <c r="D3647" s="5">
@@ -77733,20 +77742,92 @@
     </row>
     <row r="3704" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3704" t="s">
-        <v>3220</v>
+        <v>380</v>
       </c>
       <c r="B3704" t="s">
-        <v>432</v>
+        <v>1475</v>
       </c>
       <c r="C3704" t="str">
         <f t="shared" si="57"/>
-        <v>Arran Scott</v>
+        <v>Dean Hodge</v>
       </c>
       <c r="D3704" s="5">
         <v>46221</v>
       </c>
       <c r="E3704" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="3705" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3705" t="s">
+        <v>3220</v>
+      </c>
+      <c r="B3705" t="s">
+        <v>432</v>
+      </c>
+      <c r="C3705" t="str">
+        <f t="shared" si="57"/>
+        <v>Arran Scott</v>
+      </c>
+      <c r="D3705" s="5">
+        <v>46221</v>
+      </c>
+      <c r="E3705" t="s">
         <v>344</v>
+      </c>
+    </row>
+    <row r="3706" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3706" t="s">
+        <v>669</v>
+      </c>
+      <c r="B3706" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C3706" t="str">
+        <f t="shared" si="57"/>
+        <v>Ellen Skilling</v>
+      </c>
+      <c r="D3706" s="5">
+        <v>46221</v>
+      </c>
+      <c r="E3706" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="3707" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3707" t="s">
+        <v>368</v>
+      </c>
+      <c r="B3707" t="s">
+        <v>3222</v>
+      </c>
+      <c r="C3707" t="str">
+        <f t="shared" si="57"/>
+        <v>Zach Domonikibau</v>
+      </c>
+      <c r="D3707" s="5">
+        <v>46222</v>
+      </c>
+      <c r="E3707" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="3708" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3708" t="s">
+        <v>313</v>
+      </c>
+      <c r="B3708" t="s">
+        <v>3223</v>
+      </c>
+      <c r="C3708" t="str">
+        <f t="shared" si="57"/>
+        <v>Brian Mclawrence</v>
+      </c>
+      <c r="D3708" s="5">
+        <v>46223</v>
+      </c>
+      <c r="E3708" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11320" uniqueCount="3231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11342" uniqueCount="3236">
   <si>
     <t>First Name</t>
   </si>
@@ -9721,6 +9721,21 @@
   </si>
   <si>
     <t>Rafferty-McCabe</t>
+  </si>
+  <si>
+    <t>Praveen kumar</t>
+  </si>
+  <si>
+    <t>Kapala</t>
+  </si>
+  <si>
+    <t>Naveen</t>
+  </si>
+  <si>
+    <t>Shyam Sundhar</t>
+  </si>
+  <si>
+    <t>Taneni</t>
   </si>
 </sst>
 </file>
@@ -10542,7 +10557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3711"/>
+  <dimension ref="A1:F3718"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -66388,7 +66403,7 @@
         <v>46151</v>
       </c>
       <c r="E3075" t="s">
-        <v>1366</v>
+        <v>1287</v>
       </c>
       <c r="F3075" t="s">
         <v>2929</v>
@@ -73636,7 +73651,7 @@
         <v>46176</v>
       </c>
       <c r="E3476" t="s">
-        <v>1141</v>
+        <v>1704</v>
       </c>
       <c r="F3476" t="s">
         <v>1704</v>
@@ -75637,7 +75652,7 @@
         <v>46195</v>
       </c>
       <c r="E3586" t="s">
-        <v>1460</v>
+        <v>921</v>
       </c>
       <c r="F3586" t="s">
         <v>921</v>
@@ -77635,7 +77650,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="3697" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3697" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3697" t="s">
         <v>901</v>
       </c>
@@ -77653,7 +77668,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="3698" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3698" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3698" t="s">
         <v>380</v>
       </c>
@@ -77671,7 +77686,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="3699" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3699" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3699" t="s">
         <v>3219</v>
       </c>
@@ -77689,7 +77704,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="3700" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3700" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3700" t="s">
         <v>669</v>
       </c>
@@ -77707,7 +77722,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="3701" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3701" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3701" t="s">
         <v>368</v>
       </c>
@@ -77725,7 +77740,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="3702" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3702" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3702" t="s">
         <v>3224</v>
       </c>
@@ -77743,7 +77758,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="3703" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3703" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3703" t="s">
         <v>3226</v>
       </c>
@@ -77761,7 +77776,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="3704" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3704" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3704" t="s">
         <v>313</v>
       </c>
@@ -77779,7 +77794,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="3705" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3705" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3705" t="s">
         <v>885</v>
       </c>
@@ -77787,7 +77802,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3711" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3718" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -77797,7 +77812,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="3706" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3706" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3706" t="s">
         <v>356</v>
       </c>
@@ -77815,7 +77830,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="3707" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3707" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3707" t="s">
         <v>1194</v>
       </c>
@@ -77833,7 +77848,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3708" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3708" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3708" t="s">
         <v>3228</v>
       </c>
@@ -77851,7 +77866,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="3709" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3709" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3709" t="s">
         <v>221</v>
       </c>
@@ -77869,40 +77884,169 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="3710" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3710" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3710" t="s">
-        <v>394</v>
+        <v>107</v>
       </c>
       <c r="B3710" t="s">
-        <v>484</v>
+        <v>2721</v>
       </c>
       <c r="C3710" t="str">
         <f t="shared" si="58"/>
-        <v>Stuart Harrison</v>
+        <v>Kiran Chavan</v>
       </c>
       <c r="D3710" s="5">
         <v>46226</v>
       </c>
       <c r="E3710" t="s">
-        <v>2154</v>
-      </c>
-    </row>
-    <row r="3711" spans="1:5" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="F3710" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3711" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3711" t="s">
-        <v>585</v>
+        <v>394</v>
       </c>
       <c r="B3711" t="s">
-        <v>3230</v>
+        <v>484</v>
       </c>
       <c r="C3711" t="str">
         <f t="shared" si="58"/>
-        <v>Jude Rafferty-Mccabe</v>
+        <v>Stuart Harrison</v>
       </c>
       <c r="D3711" s="5">
         <v>46226</v>
       </c>
       <c r="E3711" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="3712" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3712" t="s">
+        <v>3231</v>
+      </c>
+      <c r="B3712" t="s">
+        <v>3232</v>
+      </c>
+      <c r="C3712" t="str">
+        <f t="shared" si="58"/>
+        <v>Praveen Kumar Kapala</v>
+      </c>
+      <c r="D3712" s="5">
+        <v>46226</v>
+      </c>
+      <c r="E3712" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="3713" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3713" t="s">
+        <v>3233</v>
+      </c>
+      <c r="B3713" t="s">
+        <v>831</v>
+      </c>
+      <c r="C3713" t="str">
+        <f t="shared" si="58"/>
+        <v>Naveen Patil</v>
+      </c>
+      <c r="D3713" s="5">
+        <v>46226</v>
+      </c>
+      <c r="E3713" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="3714" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3714" t="s">
+        <v>585</v>
+      </c>
+      <c r="B3714" t="s">
+        <v>3230</v>
+      </c>
+      <c r="C3714" t="str">
+        <f t="shared" si="58"/>
+        <v>Jude Rafferty-Mccabe</v>
+      </c>
+      <c r="D3714" s="5">
+        <v>46226</v>
+      </c>
+      <c r="E3714" t="s">
         <v>1460</v>
+      </c>
+    </row>
+    <row r="3715" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3715" t="s">
+        <v>419</v>
+      </c>
+      <c r="B3715" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C3715" t="str">
+        <f t="shared" si="58"/>
+        <v>Stephen Black</v>
+      </c>
+      <c r="D3715" s="5">
+        <v>46227</v>
+      </c>
+      <c r="E3715" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="3716" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3716" t="s">
+        <v>458</v>
+      </c>
+      <c r="B3716" t="s">
+        <v>460</v>
+      </c>
+      <c r="C3716" t="str">
+        <f t="shared" si="58"/>
+        <v>Imogen Brown</v>
+      </c>
+      <c r="D3716" s="5">
+        <v>46227</v>
+      </c>
+      <c r="E3716" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="3717" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3717" t="s">
+        <v>3234</v>
+      </c>
+      <c r="B3717" t="s">
+        <v>592</v>
+      </c>
+      <c r="C3717" t="str">
+        <f t="shared" si="58"/>
+        <v>Shyam Sundhar Jayakumar</v>
+      </c>
+      <c r="D3717" s="5">
+        <v>46227</v>
+      </c>
+      <c r="E3717" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="3718" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3718" t="s">
+        <v>2752</v>
+      </c>
+      <c r="B3718" t="s">
+        <v>3235</v>
+      </c>
+      <c r="C3718" t="str">
+        <f t="shared" si="58"/>
+        <v>Dinesh Taneni</v>
+      </c>
+      <c r="D3718" s="5">
+        <v>46227</v>
+      </c>
+      <c r="E3718" t="s">
+        <v>770</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11342" uniqueCount="3236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11348" uniqueCount="3236">
   <si>
     <t>First Name</t>
   </si>
@@ -10557,7 +10557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3718"/>
+  <dimension ref="A1:F3720"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -77802,7 +77802,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3718" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3720" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -78047,6 +78047,42 @@
       </c>
       <c r="E3718" t="s">
         <v>770</v>
+      </c>
+    </row>
+    <row r="3719" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3719" t="s">
+        <v>377</v>
+      </c>
+      <c r="B3719" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C3719" t="str">
+        <f t="shared" si="58"/>
+        <v>Callum O'Connor</v>
+      </c>
+      <c r="D3719" s="5">
+        <v>46228</v>
+      </c>
+      <c r="E3719" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="3720" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3720" t="s">
+        <v>337</v>
+      </c>
+      <c r="B3720" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C3720" t="str">
+        <f t="shared" si="58"/>
+        <v>Christopher Webb</v>
+      </c>
+      <c r="D3720" s="5">
+        <v>46228</v>
+      </c>
+      <c r="E3720" t="s">
+        <v>2190</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11348" uniqueCount="3236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11351" uniqueCount="3237">
   <si>
     <t>First Name</t>
   </si>
@@ -9736,6 +9736,9 @@
   </si>
   <si>
     <t>Taneni</t>
+  </si>
+  <si>
+    <t>Suzanne</t>
   </si>
 </sst>
 </file>
@@ -10557,7 +10560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3720"/>
+  <dimension ref="A1:F3721"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -77802,7 +77805,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3720" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3721" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -78083,6 +78086,24 @@
       </c>
       <c r="E3720" t="s">
         <v>2190</v>
+      </c>
+    </row>
+    <row r="3721" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3721" t="s">
+        <v>3236</v>
+      </c>
+      <c r="B3721" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C3721" t="str">
+        <f t="shared" si="58"/>
+        <v>Suzanne Lunny</v>
+      </c>
+      <c r="D3721" s="5">
+        <v>46229</v>
+      </c>
+      <c r="E3721" t="s">
+        <v>1704</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11351" uniqueCount="3237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11361" uniqueCount="3241">
   <si>
     <t>First Name</t>
   </si>
@@ -9739,6 +9739,18 @@
   </si>
   <si>
     <t>Suzanne</t>
+  </si>
+  <si>
+    <t>Danielle</t>
+  </si>
+  <si>
+    <t>Mustafa</t>
+  </si>
+  <si>
+    <t>Lola</t>
+  </si>
+  <si>
+    <t>Raphael</t>
   </si>
 </sst>
 </file>
@@ -10560,7 +10572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3721"/>
+  <dimension ref="A1:F3724"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -22734,6 +22746,9 @@
       <c r="E671" t="s">
         <v>540</v>
       </c>
+      <c r="F671" t="s">
+        <v>2190</v>
+      </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
@@ -77805,7 +77820,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3721" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3724" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -78104,6 +78119,60 @@
       </c>
       <c r="E3721" t="s">
         <v>1704</v>
+      </c>
+    </row>
+    <row r="3722" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3722" t="s">
+        <v>3237</v>
+      </c>
+      <c r="B3722" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C3722" t="str">
+        <f t="shared" si="58"/>
+        <v>Danielle Heron</v>
+      </c>
+      <c r="D3722" s="5">
+        <v>46231</v>
+      </c>
+      <c r="E3722" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3723" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3723" t="s">
+        <v>676</v>
+      </c>
+      <c r="B3723" t="s">
+        <v>3238</v>
+      </c>
+      <c r="C3723" t="str">
+        <f t="shared" si="58"/>
+        <v>Muhammad Mustafa</v>
+      </c>
+      <c r="D3723" s="5">
+        <v>46231</v>
+      </c>
+      <c r="E3723" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="3724" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3724" t="s">
+        <v>3239</v>
+      </c>
+      <c r="B3724" t="s">
+        <v>3240</v>
+      </c>
+      <c r="C3724" t="str">
+        <f t="shared" si="58"/>
+        <v>Lola Raphael</v>
+      </c>
+      <c r="D3724" s="5">
+        <v>46231</v>
+      </c>
+      <c r="E3724" t="s">
+        <v>3206</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11361" uniqueCount="3241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11387" uniqueCount="3246">
   <si>
     <t>First Name</t>
   </si>
@@ -9751,6 +9751,21 @@
   </si>
   <si>
     <t>Raphael</t>
+  </si>
+  <si>
+    <t>Cate</t>
+  </si>
+  <si>
+    <t>Mosgrove</t>
+  </si>
+  <si>
+    <t>Darwin</t>
+  </si>
+  <si>
+    <t>Antappan</t>
+  </si>
+  <si>
+    <t>Syam Kumar</t>
   </si>
 </sst>
 </file>
@@ -10572,7 +10587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3724"/>
+  <dimension ref="A1:F3732"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -77820,7 +77835,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3724" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3732" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -77959,7 +77974,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="3713" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3713" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3713" t="s">
         <v>3233</v>
       </c>
@@ -77977,7 +77992,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="3714" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3714" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3714" t="s">
         <v>585</v>
       </c>
@@ -77995,7 +78010,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="3715" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3715" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3715" t="s">
         <v>419</v>
       </c>
@@ -78013,7 +78028,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="3716" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3716" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3716" t="s">
         <v>458</v>
       </c>
@@ -78031,7 +78046,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="3717" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3717" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3717" t="s">
         <v>3234</v>
       </c>
@@ -78049,7 +78064,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="3718" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3718" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3718" t="s">
         <v>2752</v>
       </c>
@@ -78067,7 +78082,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="3719" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3719" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3719" t="s">
         <v>377</v>
       </c>
@@ -78085,7 +78100,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="3720" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3720" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3720" t="s">
         <v>337</v>
       </c>
@@ -78103,7 +78118,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="3721" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3721" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3721" t="s">
         <v>3236</v>
       </c>
@@ -78121,7 +78136,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="3722" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3722" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3722" t="s">
         <v>3237</v>
       </c>
@@ -78139,40 +78154,190 @@
         <v>540</v>
       </c>
     </row>
-    <row r="3723" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3723" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3723" t="s">
-        <v>676</v>
+        <v>3241</v>
       </c>
       <c r="B3723" t="s">
-        <v>3238</v>
+        <v>584</v>
       </c>
       <c r="C3723" t="str">
         <f t="shared" si="58"/>
-        <v>Muhammad Mustafa</v>
+        <v>Cate Hirst</v>
       </c>
       <c r="D3723" s="5">
         <v>46231</v>
       </c>
       <c r="E3723" t="s">
-        <v>1881</v>
-      </c>
-    </row>
-    <row r="3724" spans="1:5" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3724" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3724" t="s">
-        <v>3239</v>
+        <v>971</v>
       </c>
       <c r="B3724" t="s">
-        <v>3240</v>
+        <v>3242</v>
       </c>
       <c r="C3724" t="str">
         <f t="shared" si="58"/>
-        <v>Lola Raphael</v>
+        <v>Ella Mosgrove</v>
       </c>
       <c r="D3724" s="5">
         <v>46231</v>
       </c>
       <c r="E3724" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3725" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3725" t="s">
+        <v>676</v>
+      </c>
+      <c r="B3725" t="s">
+        <v>3238</v>
+      </c>
+      <c r="C3725" t="str">
+        <f t="shared" si="58"/>
+        <v>Muhammad Mustafa</v>
+      </c>
+      <c r="D3725" s="5">
+        <v>46231</v>
+      </c>
+      <c r="E3725" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="3726" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3726" t="s">
+        <v>3239</v>
+      </c>
+      <c r="B3726" t="s">
+        <v>3240</v>
+      </c>
+      <c r="C3726" t="str">
+        <f t="shared" si="58"/>
+        <v>Lola Raphael</v>
+      </c>
+      <c r="D3726" s="5">
+        <v>46231</v>
+      </c>
+      <c r="E3726" t="s">
         <v>3206</v>
+      </c>
+    </row>
+    <row r="3727" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3727" t="s">
+        <v>668</v>
+      </c>
+      <c r="B3727" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C3727" t="str">
+        <f t="shared" si="58"/>
+        <v>Charlotte Shivers</v>
+      </c>
+      <c r="D3727" s="5">
+        <v>46231</v>
+      </c>
+      <c r="E3727" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3728" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3728" t="s">
+        <v>377</v>
+      </c>
+      <c r="B3728" t="s">
+        <v>379</v>
+      </c>
+      <c r="C3728" t="str">
+        <f t="shared" si="58"/>
+        <v>Callum Gibson</v>
+      </c>
+      <c r="D3728" s="5">
+        <v>46232</v>
+      </c>
+      <c r="E3728" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F3728" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="3729" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3729" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3729" t="s">
+        <v>592</v>
+      </c>
+      <c r="C3729" t="str">
+        <f t="shared" si="58"/>
+        <v>Vishnu Jayakumar</v>
+      </c>
+      <c r="D3729" s="5">
+        <v>46232</v>
+      </c>
+      <c r="E3729" t="s">
+        <v>2190</v>
+      </c>
+      <c r="F3729" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="3730" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3730" t="s">
+        <v>331</v>
+      </c>
+      <c r="B3730" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C3730" t="str">
+        <f t="shared" si="58"/>
+        <v>Joshua Mcclune</v>
+      </c>
+      <c r="D3730" s="5">
+        <v>46232</v>
+      </c>
+      <c r="E3730" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="3731" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3731" t="s">
+        <v>3243</v>
+      </c>
+      <c r="B3731" t="s">
+        <v>3244</v>
+      </c>
+      <c r="C3731" t="str">
+        <f t="shared" si="58"/>
+        <v>Darwin Antappan</v>
+      </c>
+      <c r="D3731" s="5">
+        <v>46233</v>
+      </c>
+      <c r="E3731" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3732" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3732" t="s">
+        <v>3245</v>
+      </c>
+      <c r="B3732" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3732" t="str">
+        <f t="shared" si="58"/>
+        <v>Syam Kumar Sasidharan Nair</v>
+      </c>
+      <c r="D3732" s="5">
+        <v>46233</v>
+      </c>
+      <c r="E3732" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -12424,7 +12424,7 @@
         <v>921</v>
       </c>
       <c r="F99" t="s">
-        <v>921</v>
+        <v>859</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11387" uniqueCount="3246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11399" uniqueCount="3247">
   <si>
     <t>First Name</t>
   </si>
@@ -9766,6 +9766,9 @@
   </si>
   <si>
     <t>Syam Kumar</t>
+  </si>
+  <si>
+    <t>Jade</t>
   </si>
 </sst>
 </file>
@@ -10587,7 +10590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3732"/>
+  <dimension ref="A1:F3736"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -77835,7 +77838,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3732" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3736" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -78338,6 +78341,78 @@
       </c>
       <c r="E3732" t="s">
         <v>140</v>
+      </c>
+    </row>
+    <row r="3733" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3733" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B3733" t="s">
+        <v>525</v>
+      </c>
+      <c r="C3733" t="str">
+        <f t="shared" si="58"/>
+        <v>Barry Mullan</v>
+      </c>
+      <c r="D3733" s="5">
+        <v>46234</v>
+      </c>
+      <c r="E3733" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="3734" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3734" t="s">
+        <v>3246</v>
+      </c>
+      <c r="B3734" t="s">
+        <v>975</v>
+      </c>
+      <c r="C3734" t="str">
+        <f t="shared" si="58"/>
+        <v>Jade Neely</v>
+      </c>
+      <c r="D3734" s="5">
+        <v>46234</v>
+      </c>
+      <c r="E3734" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="3735" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3735" t="s">
+        <v>390</v>
+      </c>
+      <c r="B3735" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C3735" t="str">
+        <f t="shared" si="58"/>
+        <v>Samuel Mcconnell</v>
+      </c>
+      <c r="D3735" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E3735" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="3736" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3736" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B3736" t="s">
+        <v>626</v>
+      </c>
+      <c r="C3736" t="str">
+        <f t="shared" si="58"/>
+        <v>Paula Parker</v>
+      </c>
+      <c r="D3736" s="5">
+        <v>46235</v>
+      </c>
+      <c r="E3736" t="s">
+        <v>1986</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11399" uniqueCount="3247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11414" uniqueCount="3250">
   <si>
     <t>First Name</t>
   </si>
@@ -9769,6 +9769,15 @@
   </si>
   <si>
     <t>Jade</t>
+  </si>
+  <si>
+    <t>Boulan</t>
+  </si>
+  <si>
+    <t>Carolyn</t>
+  </si>
+  <si>
+    <t>Saji Thoonkuzhy</t>
   </si>
 </sst>
 </file>
@@ -10590,7 +10599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3736"/>
+  <dimension ref="A1:F3742"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -77838,7 +77847,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3736" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3742" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -78413,6 +78422,102 @@
       </c>
       <c r="E3736" t="s">
         <v>1986</v>
+      </c>
+    </row>
+    <row r="3737" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3737" t="s">
+        <v>279</v>
+      </c>
+      <c r="B3737" t="s">
+        <v>3247</v>
+      </c>
+      <c r="C3737" t="str">
+        <f t="shared" si="58"/>
+        <v>Craig Boulan</v>
+      </c>
+      <c r="D3737" s="5">
+        <v>46236</v>
+      </c>
+      <c r="E3737" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="3738" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3738" t="s">
+        <v>386</v>
+      </c>
+      <c r="B3738" t="s">
+        <v>3247</v>
+      </c>
+      <c r="C3738" t="str">
+        <f t="shared" si="58"/>
+        <v>Ryan Boulan</v>
+      </c>
+      <c r="D3738" s="5">
+        <v>46236</v>
+      </c>
+      <c r="E3738" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="3739" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3739" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B3739" t="s">
+        <v>402</v>
+      </c>
+      <c r="C3739" t="str">
+        <f t="shared" si="58"/>
+        <v>Carolyn Henry</v>
+      </c>
+      <c r="D3739" s="5">
+        <v>46236</v>
+      </c>
+      <c r="E3739" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="3740" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3740" t="s">
+        <v>278</v>
+      </c>
+      <c r="B3740" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C3740" t="str">
+        <f t="shared" si="58"/>
+        <v>James Hume</v>
+      </c>
+      <c r="D3740" s="5">
+        <v>46236</v>
+      </c>
+      <c r="E3740" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="3741" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3741" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B3741" t="s">
+        <v>3249</v>
+      </c>
+      <c r="C3741" t="str">
+        <f t="shared" si="58"/>
+        <v>Kurian Saji Thoonkuzhy</v>
+      </c>
+      <c r="D3741" s="5">
+        <v>46236</v>
+      </c>
+      <c r="E3741" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3742" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C3742" t="str">
+        <f t="shared" si="58"/>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11414" uniqueCount="3250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11420" uniqueCount="3252">
   <si>
     <t>First Name</t>
   </si>
@@ -9778,6 +9778,12 @@
   </si>
   <si>
     <t>Saji Thoonkuzhy</t>
+  </si>
+  <si>
+    <t>Mabel</t>
+  </si>
+  <si>
+    <t>Ly</t>
   </si>
 </sst>
 </file>
@@ -10599,7 +10605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3742"/>
+  <dimension ref="A1:F3743"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -77847,7 +77853,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3742" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3743" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -78515,9 +78521,39 @@
       </c>
     </row>
     <row r="3742" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3742" t="s">
+        <v>591</v>
+      </c>
+      <c r="B3742" t="s">
+        <v>3251</v>
+      </c>
       <c r="C3742" t="str">
         <f t="shared" si="58"/>
-        <v xml:space="preserve"> </v>
+        <v>Lucy Ly</v>
+      </c>
+      <c r="D3742" s="5">
+        <v>46237</v>
+      </c>
+      <c r="E3742" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="3743" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3743" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B3743" t="s">
+        <v>639</v>
+      </c>
+      <c r="C3743" t="str">
+        <f t="shared" si="58"/>
+        <v>Mabel Rea</v>
+      </c>
+      <c r="D3743" s="5">
+        <v>46237</v>
+      </c>
+      <c r="E3743" t="s">
+        <v>3206</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11420" uniqueCount="3252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11441" uniqueCount="3257">
   <si>
     <t>First Name</t>
   </si>
@@ -9784,6 +9784,21 @@
   </si>
   <si>
     <t>Ly</t>
+  </si>
+  <si>
+    <t>Jia</t>
+  </si>
+  <si>
+    <t>Avadhoot</t>
+  </si>
+  <si>
+    <t>Dandekar</t>
+  </si>
+  <si>
+    <t>Cillian</t>
+  </si>
+  <si>
+    <t>Mcvey</t>
   </si>
 </sst>
 </file>
@@ -10605,7 +10620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3743"/>
+  <dimension ref="A1:F3750"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -77853,7 +77868,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3743" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3750" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -78554,6 +78569,132 @@
       </c>
       <c r="E3743" t="s">
         <v>3206</v>
+      </c>
+    </row>
+    <row r="3744" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3744" t="s">
+        <v>482</v>
+      </c>
+      <c r="B3744" t="s">
+        <v>351</v>
+      </c>
+      <c r="C3744" t="str">
+        <f t="shared" si="58"/>
+        <v>Amy Atkinson</v>
+      </c>
+      <c r="D3744" s="5">
+        <v>46237</v>
+      </c>
+      <c r="E3744" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="3745" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3745" t="s">
+        <v>3252</v>
+      </c>
+      <c r="B3745" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C3745" t="str">
+        <f t="shared" si="58"/>
+        <v>Jia Kava</v>
+      </c>
+      <c r="D3745" s="5">
+        <v>46237</v>
+      </c>
+      <c r="E3745" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="3746" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3746" t="s">
+        <v>3253</v>
+      </c>
+      <c r="B3746" t="s">
+        <v>3254</v>
+      </c>
+      <c r="C3746" t="str">
+        <f t="shared" si="58"/>
+        <v>Avadhoot Dandekar</v>
+      </c>
+      <c r="D3746" s="5">
+        <v>46238</v>
+      </c>
+      <c r="E3746" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="3747" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3747" t="s">
+        <v>3255</v>
+      </c>
+      <c r="B3747" t="s">
+        <v>484</v>
+      </c>
+      <c r="C3747" t="str">
+        <f t="shared" si="58"/>
+        <v>Cillian Harrison</v>
+      </c>
+      <c r="D3747" s="5">
+        <v>46239</v>
+      </c>
+      <c r="E3747" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="3748" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3748" t="s">
+        <v>309</v>
+      </c>
+      <c r="B3748" t="s">
+        <v>3256</v>
+      </c>
+      <c r="C3748" t="str">
+        <f t="shared" si="58"/>
+        <v>Patrick Mcvey</v>
+      </c>
+      <c r="D3748" s="5">
+        <v>46239</v>
+      </c>
+      <c r="E3748" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="3749" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3749" t="s">
+        <v>3068</v>
+      </c>
+      <c r="B3749" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3749" t="str">
+        <f t="shared" si="58"/>
+        <v>Shibin Joseph</v>
+      </c>
+      <c r="D3749" s="5">
+        <v>46241</v>
+      </c>
+      <c r="E3749" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="3750" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3750" t="s">
+        <v>3209</v>
+      </c>
+      <c r="B3750" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3750" t="str">
+        <f t="shared" si="58"/>
+        <v>Tony Joseph</v>
+      </c>
+      <c r="D3750" s="5">
+        <v>46241</v>
+      </c>
+      <c r="E3750" t="s">
+        <v>1881</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11441" uniqueCount="3257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11444" uniqueCount="3257">
   <si>
     <t>First Name</t>
   </si>
@@ -10620,7 +10620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3750"/>
+  <dimension ref="A1:F3751"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -77868,7 +77868,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3750" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3751" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -78694,6 +78694,24 @@
         <v>46241</v>
       </c>
       <c r="E3750" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="3751" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3751" t="s">
+        <v>373</v>
+      </c>
+      <c r="B3751" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C3751" t="str">
+        <f t="shared" si="58"/>
+        <v>Ben Maxwell</v>
+      </c>
+      <c r="D3751" s="5">
+        <v>46241</v>
+      </c>
+      <c r="E3751" t="s">
         <v>1881</v>
       </c>
     </row>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11444" uniqueCount="3257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11450" uniqueCount="3257">
   <si>
     <t>First Name</t>
   </si>
@@ -10620,7 +10620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3751"/>
+  <dimension ref="A1:F3753"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -77868,7 +77868,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3751" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3753" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -78713,6 +78713,42 @@
       </c>
       <c r="E3751" t="s">
         <v>1881</v>
+      </c>
+    </row>
+    <row r="3752" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3752" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B3752" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C3752" t="str">
+        <f t="shared" si="58"/>
+        <v>Christina Maxwell</v>
+      </c>
+      <c r="D3752" s="5">
+        <v>46245</v>
+      </c>
+      <c r="E3752" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="3753" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3753" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3753" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3753" t="str">
+        <f t="shared" si="58"/>
+        <v>George Thomas</v>
+      </c>
+      <c r="D3753" s="5">
+        <v>46245</v>
+      </c>
+      <c r="E3753" t="s">
+        <v>2154</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D47955B-F719-47F6-94A0-48A08741EEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17580"/>
+    <workbookView xWindow="825" yWindow="1800" windowWidth="24675" windowHeight="17175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NCU_Registered_Players_20-07-26" sheetId="1" r:id="rId1"/>
@@ -18,17 +19,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NCU_Registered_Players_20-07-26'!$A$1:$F$3404</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11450" uniqueCount="3257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11465" uniqueCount="3261">
   <si>
     <t>First Name</t>
   </si>
@@ -9799,12 +9811,24 @@
   </si>
   <si>
     <t>Mcvey</t>
+  </si>
+  <si>
+    <t>Barrington</t>
+  </si>
+  <si>
+    <t>Yousaf</t>
+  </si>
+  <si>
+    <t>Thanav</t>
+  </si>
+  <si>
+    <t>Kartikrajan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -10619,8 +10643,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3753"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F3758"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -77868,7 +77892,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3753" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3758" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -78751,8 +78775,98 @@
         <v>2154</v>
       </c>
     </row>
+    <row r="3754" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3754" t="s">
+        <v>496</v>
+      </c>
+      <c r="B3754" t="s">
+        <v>3257</v>
+      </c>
+      <c r="C3754" t="str">
+        <f t="shared" si="58"/>
+        <v>Jason Barrington</v>
+      </c>
+      <c r="D3754" s="5">
+        <v>46246</v>
+      </c>
+      <c r="E3754" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="3755" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3755" t="s">
+        <v>435</v>
+      </c>
+      <c r="B3755" t="s">
+        <v>449</v>
+      </c>
+      <c r="C3755" t="str">
+        <f t="shared" si="58"/>
+        <v>Peter Wright</v>
+      </c>
+      <c r="D3755" s="5">
+        <v>46247</v>
+      </c>
+      <c r="E3755" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="3756" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3756" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B3756" t="s">
+        <v>797</v>
+      </c>
+      <c r="C3756" t="str">
+        <f t="shared" si="58"/>
+        <v>Zoe Gray</v>
+      </c>
+      <c r="D3756" s="5">
+        <v>46248</v>
+      </c>
+      <c r="E3756" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3757" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3757" t="s">
+        <v>3258</v>
+      </c>
+      <c r="B3757" t="s">
+        <v>302</v>
+      </c>
+      <c r="C3757" t="str">
+        <f t="shared" si="58"/>
+        <v>Yousaf Hussain</v>
+      </c>
+      <c r="D3757" s="5">
+        <v>46248</v>
+      </c>
+      <c r="E3757" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="3758" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3758" t="s">
+        <v>3259</v>
+      </c>
+      <c r="B3758" t="s">
+        <v>3260</v>
+      </c>
+      <c r="C3758" t="str">
+        <f t="shared" si="58"/>
+        <v>Thanav Kartikrajan</v>
+      </c>
+      <c r="D3758" s="5">
+        <v>46248</v>
+      </c>
+      <c r="E3758" t="s">
+        <v>1704</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:F3600">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F3600">
     <sortCondition ref="D2:D3600"/>
     <sortCondition ref="B2:B3600"/>
     <sortCondition ref="A2:A3600"/>
@@ -78763,7 +78877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D47955B-F719-47F6-94A0-48A08741EEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D5C2B1-35DA-488A-AD1E-72DBD457EA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="1800" windowWidth="24675" windowHeight="17175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="255" yWindow="1665" windowWidth="22185" windowHeight="17175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NCU_Registered_Players_20-07-26" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11465" uniqueCount="3261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11471" uniqueCount="3261">
   <si>
     <t>First Name</t>
   </si>
@@ -10644,7 +10644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3758"/>
+  <dimension ref="A1:F3760"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -77892,7 +77892,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3758" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3760" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -78863,6 +78863,42 @@
       </c>
       <c r="E3758" t="s">
         <v>1704</v>
+      </c>
+    </row>
+    <row r="3759" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3759" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B3759" t="s">
+        <v>3165</v>
+      </c>
+      <c r="C3759" t="str">
+        <f t="shared" si="58"/>
+        <v>Aiden Saji</v>
+      </c>
+      <c r="D3759" s="5">
+        <v>46248</v>
+      </c>
+      <c r="E3759" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="3760" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3760" t="s">
+        <v>504</v>
+      </c>
+      <c r="B3760" t="s">
+        <v>629</v>
+      </c>
+      <c r="C3760" t="str">
+        <f t="shared" si="58"/>
+        <v>Jonathan Phillips</v>
+      </c>
+      <c r="D3760" s="5">
+        <v>46249</v>
+      </c>
+      <c r="E3760" t="s">
+        <v>1986</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D5C2B1-35DA-488A-AD1E-72DBD457EA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645B2C37-73A3-465B-839D-470498A28A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="255" yWindow="1665" windowWidth="22185" windowHeight="17175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1725" yWindow="1770" windowWidth="28410" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NCU_Registered_Players_20-07-26" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11471" uniqueCount="3261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11474" uniqueCount="3261">
   <si>
     <t>First Name</t>
   </si>
@@ -10644,7 +10644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3760"/>
+  <dimension ref="A1:F3761"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
@@ -77892,7 +77892,7 @@
         <v>3218</v>
       </c>
       <c r="C3705" t="str">
-        <f t="shared" ref="C3705:C3760" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
+        <f t="shared" ref="C3705:C3761" si="58">PROPER(A3705&amp; " "&amp;B3705)</f>
         <v>Cameron Doak</v>
       </c>
       <c r="D3705" s="5">
@@ -78899,6 +78899,24 @@
       </c>
       <c r="E3760" t="s">
         <v>1986</v>
+      </c>
+    </row>
+    <row r="3761" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3761" t="s">
+        <v>459</v>
+      </c>
+      <c r="B3761" t="s">
+        <v>420</v>
+      </c>
+      <c r="C3761" t="str">
+        <f t="shared" si="58"/>
+        <v>Anna Murray</v>
+      </c>
+      <c r="D3761" s="5">
+        <v>46250</v>
+      </c>
+      <c r="E3761" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF75904-7704-4268-B1AB-85C48C105A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B7C888-AB4C-423E-A85A-333BB1DB4ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15645" yWindow="4665" windowWidth="20085" windowHeight="16335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="630" yWindow="1725" windowWidth="21165" windowHeight="16335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11477" uniqueCount="3261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11478" uniqueCount="3262">
   <si>
     <t>First Name</t>
   </si>
@@ -9816,6 +9816,9 @@
   </si>
   <si>
     <t>NIMA CC</t>
+  </si>
+  <si>
+    <t>Transfer Date</t>
   </si>
 </sst>
 </file>
@@ -9859,7 +9862,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9868,6 +9871,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10172,18 +10176,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3761"/>
+  <dimension ref="A1:G3761"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10202,8 +10207,11 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="2" t="s">
+        <v>3261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -10221,7 +10229,7 @@
         <v>3205</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -10239,7 +10247,7 @@
         <v>3206</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -10257,7 +10265,7 @@
         <v>3207</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -10275,7 +10283,7 @@
         <v>3208</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -10293,7 +10301,7 @@
         <v>3208</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -10314,7 +10322,7 @@
         <v>3205</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -10335,7 +10343,7 @@
         <v>3209</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -10353,7 +10361,7 @@
         <v>3206</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -10374,7 +10382,7 @@
         <v>3233</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -10395,7 +10403,7 @@
         <v>3224</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -10416,7 +10424,7 @@
         <v>3205</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -10434,7 +10442,7 @@
         <v>3211</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -10455,7 +10463,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -10473,7 +10481,7 @@
         <v>3213</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -75825,7 +75833,7 @@
         <v>3241</v>
       </c>
     </row>
-    <row r="3617" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3617" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3617" t="s">
         <v>1407</v>
       </c>
@@ -75843,7 +75851,7 @@
         <v>3217</v>
       </c>
     </row>
-    <row r="3618" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3618" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3618" t="s">
         <v>282</v>
       </c>
@@ -75861,7 +75869,7 @@
         <v>3223</v>
       </c>
     </row>
-    <row r="3619" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3619" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3619" t="s">
         <v>1408</v>
       </c>
@@ -75879,7 +75887,7 @@
         <v>3236</v>
       </c>
     </row>
-    <row r="3620" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3620" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3620" t="s">
         <v>71</v>
       </c>
@@ -75897,7 +75905,7 @@
         <v>3213</v>
       </c>
     </row>
-    <row r="3621" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3621" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3621" t="s">
         <v>1409</v>
       </c>
@@ -75915,7 +75923,7 @@
         <v>3207</v>
       </c>
     </row>
-    <row r="3622" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3622" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3622" t="s">
         <v>994</v>
       </c>
@@ -75933,7 +75941,7 @@
         <v>3210</v>
       </c>
     </row>
-    <row r="3623" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3623" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3623" t="s">
         <v>951</v>
       </c>
@@ -75951,7 +75959,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="3624" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3624" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3624" t="s">
         <v>8</v>
       </c>
@@ -75969,7 +75977,7 @@
         <v>3210</v>
       </c>
     </row>
-    <row r="3625" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3625" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3625" t="s">
         <v>82</v>
       </c>
@@ -75987,7 +75995,7 @@
         <v>3240</v>
       </c>
     </row>
-    <row r="3626" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3626" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3626" t="s">
         <v>238</v>
       </c>
@@ -76005,7 +76013,7 @@
         <v>3212</v>
       </c>
     </row>
-    <row r="3627" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3627" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3627" t="s">
         <v>168</v>
       </c>
@@ -76023,7 +76031,7 @@
         <v>3212</v>
       </c>
     </row>
-    <row r="3628" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3628" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3628" t="s">
         <v>1410</v>
       </c>
@@ -76043,8 +76051,11 @@
       <c r="F3628" t="s">
         <v>3229</v>
       </c>
-    </row>
-    <row r="3629" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3628" s="4">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="3629" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3629" t="s">
         <v>1411</v>
       </c>
@@ -76062,7 +76073,7 @@
         <v>3210</v>
       </c>
     </row>
-    <row r="3630" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3630" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3630" t="s">
         <v>1412</v>
       </c>
@@ -76080,7 +76091,7 @@
         <v>3211</v>
       </c>
     </row>
-    <row r="3631" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3631" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3631" t="s">
         <v>190</v>
       </c>
@@ -76098,7 +76109,7 @@
         <v>3229</v>
       </c>
     </row>
-    <row r="3632" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3632" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3632" t="s">
         <v>1413</v>
       </c>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B7C888-AB4C-423E-A85A-333BB1DB4ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B369D2A-D4B7-49B7-906B-025A6CB7CE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="1725" windowWidth="21165" windowHeight="16335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="660" windowWidth="18690" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11478" uniqueCount="3262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11496" uniqueCount="3265">
   <si>
     <t>First Name</t>
   </si>
@@ -9819,6 +9819,15 @@
   </si>
   <si>
     <t>Transfer Date</t>
+  </si>
+  <si>
+    <t>Paddy</t>
+  </si>
+  <si>
+    <t>Shahbaz</t>
+  </si>
+  <si>
+    <t>Umar Jalal Bhandara</t>
   </si>
 </sst>
 </file>
@@ -10176,7 +10185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3761"/>
+  <dimension ref="A1:G3767"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
@@ -77623,7 +77632,7 @@
         <v>2503</v>
       </c>
       <c r="C3715" t="str">
-        <f t="shared" ref="C3715:C3761" si="58">PROPER(A3715&amp; " "&amp;B3715)</f>
+        <f t="shared" ref="C3715:C3767" si="58">PROPER(A3715&amp; " "&amp;B3715)</f>
         <v>Stephen Black</v>
       </c>
       <c r="D3715" s="1">
@@ -78465,6 +78474,114 @@
       </c>
       <c r="E3761" t="s">
         <v>3211</v>
+      </c>
+    </row>
+    <row r="3762" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3762" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3762" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C3762" t="str">
+        <f t="shared" si="58"/>
+        <v>Josh Brown</v>
+      </c>
+      <c r="D3762" s="1">
+        <v>46254</v>
+      </c>
+      <c r="E3762" t="s">
+        <v>3252</v>
+      </c>
+    </row>
+    <row r="3763" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3763" t="s">
+        <v>3262</v>
+      </c>
+      <c r="B3763" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C3763" t="str">
+        <f t="shared" si="58"/>
+        <v>Paddy Brown</v>
+      </c>
+      <c r="D3763" s="1">
+        <v>46254</v>
+      </c>
+      <c r="E3763" t="s">
+        <v>3252</v>
+      </c>
+    </row>
+    <row r="3764" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3764" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3764" t="s">
+        <v>2430</v>
+      </c>
+      <c r="C3764" t="str">
+        <f t="shared" si="58"/>
+        <v>Patrick Smith</v>
+      </c>
+      <c r="D3764" s="1">
+        <v>46254</v>
+      </c>
+      <c r="E3764" t="s">
+        <v>3252</v>
+      </c>
+    </row>
+    <row r="3765" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3765" t="s">
+        <v>3263</v>
+      </c>
+      <c r="B3765" t="s">
+        <v>3264</v>
+      </c>
+      <c r="C3765" t="str">
+        <f t="shared" si="58"/>
+        <v>Shahbaz Umar Jalal Bhandara</v>
+      </c>
+      <c r="D3765" s="1">
+        <v>46254</v>
+      </c>
+      <c r="E3765" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="3766" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3766" t="s">
+        <v>989</v>
+      </c>
+      <c r="B3766" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C3766" t="str">
+        <f t="shared" si="58"/>
+        <v>Mike Jones</v>
+      </c>
+      <c r="D3766" s="1">
+        <v>46255</v>
+      </c>
+      <c r="E3766" t="s">
+        <v>3229</v>
+      </c>
+    </row>
+    <row r="3767" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3767" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B3767" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C3767" t="str">
+        <f t="shared" si="58"/>
+        <v>Aditya Pawar</v>
+      </c>
+      <c r="D3767" s="1">
+        <v>46255</v>
+      </c>
+      <c r="E3767" t="s">
+        <v>3216</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B369D2A-D4B7-49B7-906B-025A6CB7CE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174E9855-B33A-4C79-A7ED-55675D700FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="660" windowWidth="18690" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="825" yWindow="480" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11496" uniqueCount="3265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11502" uniqueCount="3266">
   <si>
     <t>First Name</t>
   </si>
@@ -9828,6 +9828,9 @@
   </si>
   <si>
     <t>Umar Jalal Bhandara</t>
+  </si>
+  <si>
+    <t>Aadhidev</t>
   </si>
 </sst>
 </file>
@@ -10185,7 +10188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3767"/>
+  <dimension ref="A1:G3769"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
@@ -77632,7 +77635,7 @@
         <v>2503</v>
       </c>
       <c r="C3715" t="str">
-        <f t="shared" ref="C3715:C3767" si="58">PROPER(A3715&amp; " "&amp;B3715)</f>
+        <f t="shared" ref="C3715:C3769" si="58">PROPER(A3715&amp; " "&amp;B3715)</f>
         <v>Stephen Black</v>
       </c>
       <c r="D3715" s="1">
@@ -78582,6 +78585,42 @@
       </c>
       <c r="E3767" t="s">
         <v>3216</v>
+      </c>
+    </row>
+    <row r="3768" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3768" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3768" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C3768" t="str">
+        <f t="shared" si="58"/>
+        <v>Gavin Mckenna</v>
+      </c>
+      <c r="D3768" s="1">
+        <v>46256</v>
+      </c>
+      <c r="E3768" t="s">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="3769" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3769" t="s">
+        <v>3265</v>
+      </c>
+      <c r="B3769" t="s">
+        <v>976</v>
+      </c>
+      <c r="C3769" t="str">
+        <f t="shared" si="58"/>
+        <v>Aadhidev Praveenraj</v>
+      </c>
+      <c r="D3769" s="1">
+        <v>46256</v>
+      </c>
+      <c r="E3769" t="s">
+        <v>3241</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174E9855-B33A-4C79-A7ED-55675D700FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8712F3-9FE0-40C3-9A45-E511D168E8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="480" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4260" yWindow="315" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45296,7 +45296,7 @@
         <v>3232</v>
       </c>
     </row>
-    <row r="1937" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1937" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1937" t="s">
         <v>904</v>
       </c>
@@ -45314,7 +45314,7 @@
         <v>3205</v>
       </c>
     </row>
-    <row r="1938" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1938" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1938" t="s">
         <v>135</v>
       </c>
@@ -45334,8 +45334,11 @@
       <c r="F1938" t="s">
         <v>3207</v>
       </c>
-    </row>
-    <row r="1939" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1938" s="4">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1939" t="s">
         <v>280</v>
       </c>
@@ -45353,7 +45356,7 @@
         <v>3240</v>
       </c>
     </row>
-    <row r="1940" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1940" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1940" t="s">
         <v>905</v>
       </c>
@@ -45371,7 +45374,7 @@
         <v>3240</v>
       </c>
     </row>
-    <row r="1941" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1941" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1941" t="s">
         <v>203</v>
       </c>
@@ -45389,7 +45392,7 @@
         <v>3222</v>
       </c>
     </row>
-    <row r="1942" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1942" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1942" t="s">
         <v>79</v>
       </c>
@@ -45410,7 +45413,7 @@
         <v>3223</v>
       </c>
     </row>
-    <row r="1943" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1943" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1943" t="s">
         <v>906</v>
       </c>
@@ -45428,7 +45431,7 @@
         <v>3231</v>
       </c>
     </row>
-    <row r="1944" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1944" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1944" t="s">
         <v>907</v>
       </c>
@@ -45446,7 +45449,7 @@
         <v>3233</v>
       </c>
     </row>
-    <row r="1945" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1945" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1945" t="s">
         <v>908</v>
       </c>
@@ -45464,7 +45467,7 @@
         <v>3236</v>
       </c>
     </row>
-    <row r="1946" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1946" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1946" t="s">
         <v>909</v>
       </c>
@@ -45482,7 +45485,7 @@
         <v>3237</v>
       </c>
     </row>
-    <row r="1947" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1947" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1947" t="s">
         <v>79</v>
       </c>
@@ -45500,7 +45503,7 @@
         <v>3237</v>
       </c>
     </row>
-    <row r="1948" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1948" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1948" t="s">
         <v>910</v>
       </c>
@@ -45518,7 +45521,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="1949" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1949" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1949" t="s">
         <v>911</v>
       </c>
@@ -45536,7 +45539,7 @@
         <v>3225</v>
       </c>
     </row>
-    <row r="1950" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1950" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1950" t="s">
         <v>912</v>
       </c>
@@ -45554,7 +45557,7 @@
         <v>3220</v>
       </c>
     </row>
-    <row r="1951" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1951" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1951" t="s">
         <v>913</v>
       </c>
@@ -45572,7 +45575,7 @@
         <v>3236</v>
       </c>
     </row>
-    <row r="1952" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1952" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1952" t="s">
         <v>914</v>
       </c>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6D14F4-F775-4442-849D-BCDFB970D683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB75D83-73FD-4AEA-BE7F-4A19EBB718BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11403" uniqueCount="3258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11406" uniqueCount="3258">
   <si>
     <t>First Name</t>
   </si>
@@ -10164,7 +10164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3767"/>
+  <dimension ref="A1:G3768"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
@@ -77322,7 +77322,7 @@
         <v>2503</v>
       </c>
       <c r="C3714" t="str">
-        <f t="shared" ref="C3714:C3767" si="58">PROPER(A3714&amp; " "&amp;B3714)</f>
+        <f t="shared" ref="C3714:C3768" si="58">PROPER(A3714&amp; " "&amp;B3714)</f>
         <v>Stephen Black</v>
       </c>
       <c r="D3714" s="1">
@@ -78287,6 +78287,24 @@
       </c>
       <c r="E3767" t="s">
         <v>3241</v>
+      </c>
+    </row>
+    <row r="3768" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3768" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B3768" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C3768" t="str">
+        <f t="shared" si="58"/>
+        <v>Farhan Rakeeb</v>
+      </c>
+      <c r="D3768" s="1">
+        <v>46257</v>
+      </c>
+      <c r="E3768" t="s">
+        <v>3216</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD06A38-5684-4CEA-882D-32B470DDE9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE91438-1B5A-4D86-AEC1-A650B05937B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="495" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="675" windowWidth="31365" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -10173,14 +10173,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.42578125" style="6" customWidth="1"/>
     <col min="8" max="8" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D09DC95-6F7F-4FCA-A16F-DBE58A52270B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BB2CA4-77C3-471D-9BDF-3FB958CFB4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="8235" windowWidth="32700" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="450" yWindow="420" windowWidth="25980" windowHeight="19590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15101" uniqueCount="6993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15116" uniqueCount="6998">
   <si>
     <t>First Name</t>
   </si>
@@ -21012,6 +21012,21 @@
   </si>
   <si>
     <t>James Magee Jnr</t>
+  </si>
+  <si>
+    <t>Bryan</t>
+  </si>
+  <si>
+    <t>Indudhar</t>
+  </si>
+  <si>
+    <t>Gurappa Jagadeesh</t>
+  </si>
+  <si>
+    <t>Priyakanth</t>
+  </si>
+  <si>
+    <t>Vaddi</t>
   </si>
 </sst>
 </file>
@@ -21377,7 +21392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3768"/>
+  <dimension ref="A1:K3773"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" bestFit="1" customWidth="1"/>
@@ -99582,7 +99597,7 @@
         <v>2502</v>
       </c>
       <c r="C3715" t="str">
-        <f t="shared" ref="C3715:C3768" si="60">PROPER(A3715&amp; " "&amp;B3715)</f>
+        <f t="shared" ref="C3715:C3773" si="60">PROPER(A3715&amp; " "&amp;B3715)</f>
         <v>Stephen Black</v>
       </c>
       <c r="D3715" s="1">
@@ -100706,6 +100721,96 @@
       </c>
       <c r="K3768" t="s">
         <v>6986</v>
+      </c>
+    </row>
+    <row r="3769" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3769" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3769" t="s">
+        <v>6993</v>
+      </c>
+      <c r="C3769" t="str">
+        <f t="shared" si="60"/>
+        <v>Sam Bryan</v>
+      </c>
+      <c r="D3769" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E3769" t="s">
+        <v>3211</v>
+      </c>
+    </row>
+    <row r="3770" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3770" t="s">
+        <v>6994</v>
+      </c>
+      <c r="B3770" t="s">
+        <v>6995</v>
+      </c>
+      <c r="C3770" t="str">
+        <f t="shared" si="60"/>
+        <v>Indudhar Gurappa Jagadeesh</v>
+      </c>
+      <c r="D3770" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E3770" t="s">
+        <v>3215</v>
+      </c>
+    </row>
+    <row r="3771" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3771" t="s">
+        <v>761</v>
+      </c>
+      <c r="B3771" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C3771" t="str">
+        <f t="shared" si="60"/>
+        <v>Prasanth Kumar</v>
+      </c>
+      <c r="D3771" s="1">
+        <v>46262</v>
+      </c>
+      <c r="E3771" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="3772" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3772" t="s">
+        <v>6996</v>
+      </c>
+      <c r="B3772" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C3772" t="str">
+        <f t="shared" si="60"/>
+        <v>Priyakanth K</v>
+      </c>
+      <c r="D3772" s="1">
+        <v>46264</v>
+      </c>
+      <c r="E3772" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="3773" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3773" t="s">
+        <v>2444</v>
+      </c>
+      <c r="B3773" t="s">
+        <v>6997</v>
+      </c>
+      <c r="C3773" t="str">
+        <f t="shared" si="60"/>
+        <v>Ravikumar Vaddi</v>
+      </c>
+      <c r="D3773" s="1">
+        <v>46264</v>
+      </c>
+      <c r="E3773" t="s">
+        <v>3235</v>
       </c>
     </row>
   </sheetData>

--- a/1. NCU_Registered_Players.xlsx
+++ b/1. NCU_Registered_Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BB2CA4-77C3-471D-9BDF-3FB958CFB4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C6F82D-4D94-44FA-9CC0-337DCFCB5F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="450" yWindow="420" windowWidth="25980" windowHeight="19590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="33810" windowHeight="19590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15116" uniqueCount="6998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15121" uniqueCount="7003">
   <si>
     <t>First Name</t>
   </si>
@@ -21027,6 +21027,21 @@
   </si>
   <si>
     <t>Vaddi</t>
+  </si>
+  <si>
+    <t>Sam Bryan</t>
+  </si>
+  <si>
+    <t>Indudhar Gurappa Jagadeesh</t>
+  </si>
+  <si>
+    <t>Prasanth Kumar</t>
+  </si>
+  <si>
+    <t>Priyakanth K</t>
+  </si>
+  <si>
+    <t>Ravikumar Vaddi</t>
   </si>
 </sst>
 </file>
@@ -100740,6 +100755,9 @@
       <c r="E3769" t="s">
         <v>3211</v>
       </c>
+      <c r="K3769" t="s">
+        <v>6998</v>
+      </c>
     </row>
     <row r="3770" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3770" t="s">
@@ -100758,6 +100776,9 @@
       <c r="E3770" t="s">
         <v>3215</v>
       </c>
+      <c r="K3770" t="s">
+        <v>6999</v>
+      </c>
     </row>
     <row r="3771" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3771" t="s">
@@ -100776,6 +100797,9 @@
       <c r="E3771" t="s">
         <v>3235</v>
       </c>
+      <c r="K3771" t="s">
+        <v>7000</v>
+      </c>
     </row>
     <row r="3772" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3772" t="s">
@@ -100794,6 +100818,9 @@
       <c r="E3772" t="s">
         <v>3235</v>
       </c>
+      <c r="K3772" t="s">
+        <v>7001</v>
+      </c>
     </row>
     <row r="3773" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3773" t="s">
@@ -100811,6 +100838,9 @@
       </c>
       <c r="E3773" t="s">
         <v>3235</v>
+      </c>
+      <c r="K3773" t="s">
+        <v>7002</v>
       </c>
     </row>
   </sheetData>
